--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation-urine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation-urine.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
